--- a/public/tally_templates/STSE.xlsx
+++ b/public/tally_templates/STSE.xlsx
@@ -1371,7 +1371,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac x16r2">
   <numFmts count="8">
     <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * -#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* (#,##0);_(* &quot;-&quot;_);_(@_)"/>
@@ -3024,7 +3024,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="458">
+  <cellXfs count="491">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -4365,6 +4365,105 @@
     <xf numFmtId="171" fontId="39" fillId="0" borderId="102" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="101" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4372,11 +4471,11 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <ns3:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <ns4:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -4732,7 +4831,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y176"/>
   <sheetFormatPr defaultRowHeight="17.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
@@ -5494,14 +5593,14 @@
       <c r="D7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="168" t="s">
         <v>60</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="207">
+      <c r="H7" s="473">
         <v>46219</v>
       </c>
       <c r="I7" s="8"/>
@@ -5531,14 +5630,14 @@
       <c r="D8" s="388" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="168">
         <v>7</v>
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="168" t="s">
         <v>154</v>
       </c>
       <c r="I8" s="8"/>
@@ -6740,14 +6839,14 @@
       <c r="D51" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E51" s="8" t="s">
+      <c r="E51" s="168" t="s">
         <v>60</v>
       </c>
       <c r="F51" s="8"/>
       <c r="G51" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="H51" s="207">
+      <c r="H51" s="473">
         <v>46219</v>
       </c>
       <c r="I51" s="8"/>
@@ -6777,14 +6876,14 @@
       <c r="D52" s="388" t="s">
         <v>7</v>
       </c>
-      <c r="E52" s="8">
+      <c r="E52" s="168">
         <v>7</v>
       </c>
       <c r="F52" s="8"/>
       <c r="G52" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="H52" s="8" t="s">
+      <c r="H52" s="168" t="s">
         <v>154</v>
       </c>
       <c r="I52" s="8"/>
@@ -6909,27 +7008,17 @@
       <c r="Y55" s="95"/>
     </row>
     <row r="56" ht="19.9" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="395" t="s">
-        <v>165</v>
-      </c>
+      <c r="A56" s="395"/>
       <c r="B56" s="396"/>
-      <c r="C56" s="397" t="s">
-        <v>166</v>
-      </c>
+      <c r="C56" s="397"/>
       <c r="D56" s="396"/>
       <c r="E56" s="396"/>
-      <c r="F56" s="398">
-        <v>-8</v>
-      </c>
-      <c r="G56" s="398">
-        <v>-8.3</v>
-      </c>
+      <c r="F56" s="398"/>
+      <c r="G56" s="398"/>
       <c r="H56" s="399" t="s">
         <v>167</v>
       </c>
-      <c r="I56" s="400" t="s">
-        <v>168</v>
-      </c>
+      <c r="I56" s="400"/>
       <c r="J56" s="42"/>
       <c r="K56" s="42"/>
       <c r="L56" s="42"/>
@@ -6948,27 +7037,15 @@
       <c r="Y56" s="42"/>
     </row>
     <row r="57" ht="19.9" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="401" t="s">
-        <v>169</v>
-      </c>
+      <c r="A57" s="401"/>
       <c r="B57" s="402"/>
-      <c r="C57" s="403" t="s">
-        <v>166</v>
-      </c>
+      <c r="C57" s="403"/>
       <c r="D57" s="402"/>
       <c r="E57" s="402"/>
-      <c r="F57" s="404">
-        <v>-19</v>
-      </c>
-      <c r="G57" s="404">
-        <v>-19</v>
-      </c>
-      <c r="H57" s="405" t="s">
-        <v>170</v>
-      </c>
-      <c r="I57" s="406" t="s">
-        <v>168</v>
-      </c>
+      <c r="F57" s="404"/>
+      <c r="G57" s="404"/>
+      <c r="H57" s="405"/>
+      <c r="I57" s="406"/>
       <c r="J57" s="42"/>
       <c r="K57" s="42"/>
       <c r="L57" s="42"/>
@@ -6987,27 +7064,15 @@
       <c r="Y57" s="42"/>
     </row>
     <row r="58" ht="19.9" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="401" t="s">
-        <v>171</v>
-      </c>
+      <c r="A58" s="401"/>
       <c r="B58" s="402"/>
-      <c r="C58" s="403" t="s">
-        <v>166</v>
-      </c>
+      <c r="C58" s="403"/>
       <c r="D58" s="402"/>
       <c r="E58" s="402"/>
-      <c r="F58" s="407">
-        <v>-18</v>
-      </c>
-      <c r="G58" s="407">
-        <v>-18.5</v>
-      </c>
-      <c r="H58" s="405" t="s">
-        <v>170</v>
-      </c>
-      <c r="I58" s="406" t="s">
-        <v>168</v>
-      </c>
+      <c r="F58" s="407"/>
+      <c r="G58" s="407"/>
+      <c r="H58" s="405"/>
+      <c r="I58" s="406"/>
       <c r="J58" s="42"/>
       <c r="K58" s="42"/>
       <c r="L58" s="42"/>
@@ -7026,27 +7091,15 @@
       <c r="Y58" s="42"/>
     </row>
     <row r="59" ht="19.9" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="401" t="s">
-        <v>172</v>
-      </c>
+      <c r="A59" s="401"/>
       <c r="B59" s="402"/>
-      <c r="C59" s="403" t="s">
-        <v>166</v>
-      </c>
+      <c r="C59" s="403"/>
       <c r="D59" s="402"/>
       <c r="E59" s="402"/>
-      <c r="F59" s="404">
-        <v>-18</v>
-      </c>
-      <c r="G59" s="404">
-        <v>-18.2</v>
-      </c>
-      <c r="H59" s="405" t="s">
-        <v>170</v>
-      </c>
-      <c r="I59" s="406" t="s">
-        <v>168</v>
-      </c>
+      <c r="F59" s="404"/>
+      <c r="G59" s="404"/>
+      <c r="H59" s="405"/>
+      <c r="I59" s="406"/>
       <c r="J59" s="42"/>
       <c r="K59" s="42"/>
       <c r="L59" s="42"/>
@@ -7065,27 +7118,15 @@
       <c r="Y59" s="42"/>
     </row>
     <row r="60" ht="19.9" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="408" t="s">
-        <v>173</v>
-      </c>
+      <c r="A60" s="408"/>
       <c r="B60" s="409"/>
-      <c r="C60" s="410" t="s">
-        <v>166</v>
-      </c>
+      <c r="C60" s="410"/>
       <c r="D60" s="409"/>
       <c r="E60" s="409"/>
-      <c r="F60" s="411">
-        <v>-18</v>
-      </c>
-      <c r="G60" s="411">
-        <v>-18.4</v>
-      </c>
-      <c r="H60" s="412" t="s">
-        <v>170</v>
-      </c>
-      <c r="I60" s="413" t="s">
-        <v>72</v>
-      </c>
+      <c r="F60" s="411"/>
+      <c r="G60" s="411"/>
+      <c r="H60" s="412"/>
+      <c r="I60" s="413"/>
       <c r="J60" s="42"/>
       <c r="K60" s="42"/>
       <c r="L60" s="42"/>
@@ -7104,27 +7145,15 @@
       <c r="Y60" s="42"/>
     </row>
     <row r="61" ht="19.9" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="395" t="s">
-        <v>174</v>
-      </c>
+      <c r="A61" s="395"/>
       <c r="B61" s="396"/>
-      <c r="C61" s="397" t="s">
-        <v>166</v>
-      </c>
+      <c r="C61" s="397"/>
       <c r="D61" s="396"/>
       <c r="E61" s="396"/>
-      <c r="F61" s="398">
-        <v>-18</v>
-      </c>
-      <c r="G61" s="398">
-        <v>-18.3</v>
-      </c>
-      <c r="H61" s="399" t="s">
-        <v>170</v>
-      </c>
-      <c r="I61" s="400" t="s">
-        <v>72</v>
-      </c>
+      <c r="F61" s="398"/>
+      <c r="G61" s="398"/>
+      <c r="H61" s="399"/>
+      <c r="I61" s="400"/>
       <c r="J61" s="42"/>
       <c r="K61" s="42"/>
       <c r="L61" s="42"/>
@@ -7143,27 +7172,15 @@
       <c r="Y61" s="42"/>
     </row>
     <row r="62" ht="19.9" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="401" t="s">
-        <v>175</v>
-      </c>
+      <c r="A62" s="401"/>
       <c r="B62" s="402"/>
-      <c r="C62" s="403" t="s">
-        <v>166</v>
-      </c>
+      <c r="C62" s="403"/>
       <c r="D62" s="402"/>
       <c r="E62" s="402"/>
-      <c r="F62" s="404">
-        <v>-2.5</v>
-      </c>
-      <c r="G62" s="404">
-        <v>-3.1</v>
-      </c>
-      <c r="H62" s="405" t="s">
-        <v>170</v>
-      </c>
-      <c r="I62" s="406" t="s">
-        <v>72</v>
-      </c>
+      <c r="F62" s="404"/>
+      <c r="G62" s="404"/>
+      <c r="H62" s="405"/>
+      <c r="I62" s="406"/>
       <c r="J62" s="42"/>
       <c r="K62" s="42"/>
       <c r="L62" s="42"/>
@@ -7182,27 +7199,15 @@
       <c r="Y62" s="42"/>
     </row>
     <row r="63" ht="19.9" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="401" t="s">
-        <v>176</v>
-      </c>
+      <c r="A63" s="401"/>
       <c r="B63" s="402"/>
-      <c r="C63" s="403" t="s">
-        <v>166</v>
-      </c>
+      <c r="C63" s="403"/>
       <c r="D63" s="402"/>
       <c r="E63" s="402"/>
-      <c r="F63" s="404">
-        <v>-18</v>
-      </c>
-      <c r="G63" s="404">
-        <v>-18.5</v>
-      </c>
-      <c r="H63" s="405" t="s">
-        <v>170</v>
-      </c>
-      <c r="I63" s="406" t="s">
-        <v>72</v>
-      </c>
+      <c r="F63" s="404"/>
+      <c r="G63" s="404"/>
+      <c r="H63" s="405"/>
+      <c r="I63" s="406"/>
       <c r="J63" s="42"/>
       <c r="K63" s="42"/>
       <c r="L63" s="42"/>
@@ -7221,27 +7226,15 @@
       <c r="Y63" s="42"/>
     </row>
     <row r="64" ht="19.9" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="401" t="s">
-        <v>177</v>
-      </c>
+      <c r="A64" s="401"/>
       <c r="B64" s="402"/>
-      <c r="C64" s="403" t="s">
-        <v>166</v>
-      </c>
+      <c r="C64" s="403"/>
       <c r="D64" s="402"/>
       <c r="E64" s="402"/>
-      <c r="F64" s="404">
-        <v>-18</v>
-      </c>
-      <c r="G64" s="404">
-        <v>-18.3</v>
-      </c>
-      <c r="H64" s="405" t="s">
-        <v>170</v>
-      </c>
-      <c r="I64" s="406" t="s">
-        <v>72</v>
-      </c>
+      <c r="F64" s="404"/>
+      <c r="G64" s="404"/>
+      <c r="H64" s="405"/>
+      <c r="I64" s="406"/>
       <c r="J64" s="42"/>
       <c r="K64" s="42"/>
       <c r="L64" s="42"/>
@@ -8106,14 +8099,14 @@
       <c r="D95" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E95" s="8" t="s">
+      <c r="E95" s="168" t="s">
         <v>79</v>
       </c>
       <c r="F95" s="8"/>
       <c r="G95" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="H95" s="207">
+      <c r="H95" s="473">
         <v>46220</v>
       </c>
       <c r="I95" s="8"/>
@@ -8151,7 +8144,7 @@
       <c r="G96" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="H96" s="8" t="s">
+      <c r="H96" s="168" t="s">
         <v>154</v>
       </c>
       <c r="I96" s="8"/>
@@ -8276,27 +8269,17 @@
       <c r="Y99" s="95"/>
     </row>
     <row r="100" ht="19.9" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="395" t="s">
-        <v>185</v>
-      </c>
+      <c r="A100" s="395"/>
       <c r="B100" s="396"/>
-      <c r="C100" s="397" t="s">
-        <v>166</v>
-      </c>
+      <c r="C100" s="397"/>
       <c r="D100" s="396"/>
       <c r="E100" s="396"/>
-      <c r="F100" s="398">
-        <v>24</v>
-      </c>
-      <c r="G100" s="398">
-        <v>24.1</v>
-      </c>
+      <c r="F100" s="398"/>
+      <c r="G100" s="398"/>
       <c r="H100" s="399" t="s">
         <v>186</v>
       </c>
-      <c r="I100" s="400" t="s">
-        <v>72</v>
-      </c>
+      <c r="I100" s="400"/>
       <c r="J100" s="42"/>
       <c r="K100" s="42"/>
       <c r="L100" s="42"/>
@@ -9552,7 +9535,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -10281,7 +10264,7 @@
       <c r="A6" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="472" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="3"/>
@@ -10293,7 +10276,7 @@
         <v>38</v>
       </c>
       <c r="I6" s="8"/>
-      <c r="J6" s="8" t="s">
+      <c r="J6" s="168" t="s">
         <v>79</v>
       </c>
       <c r="K6" s="8"/>
@@ -10303,7 +10286,7 @@
       <c r="O6" s="190" t="s">
         <v>61</v>
       </c>
-      <c r="P6" s="207">
+      <c r="P6" s="473">
         <v>46220</v>
       </c>
       <c r="Q6" s="8"/>
@@ -10347,7 +10330,7 @@
       <c r="A8" s="190" t="s">
         <v>62</v>
       </c>
-      <c r="B8" s="190" t="s">
+      <c r="B8" s="168" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="190"/>
@@ -10359,7 +10342,7 @@
         <v>80</v>
       </c>
       <c r="I8" s="8"/>
-      <c r="J8" s="8" t="s">
+      <c r="J8" s="168" t="s">
         <v>64</v>
       </c>
       <c r="K8" s="8"/>
@@ -10369,7 +10352,7 @@
       <c r="O8" s="190" t="s">
         <v>81</v>
       </c>
-      <c r="P8" s="8">
+      <c r="P8" s="168">
         <v>7</v>
       </c>
       <c r="Q8" s="8"/>
@@ -10409,7 +10392,7 @@
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
     </row>
-    <row r="10" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="211" t="s">
         <v>11</v>
       </c>
@@ -10450,7 +10433,7 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
     </row>
-    <row r="11" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="215"/>
       <c r="B11" s="215"/>
       <c r="C11" s="264"/>
@@ -10480,32 +10463,18 @@
       <c r="Y11" s="3"/>
     </row>
     <row r="12" ht="22.15" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A12" s="55" t="s">
-        <v>83</v>
-      </c>
-      <c r="B12" s="55" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" s="288" t="s">
-        <v>84</v>
-      </c>
+      <c r="A12" s="55"/>
+      <c r="B12" s="55"/>
+      <c r="C12" s="288"/>
       <c r="D12" s="289"/>
       <c r="E12" s="290"/>
-      <c r="F12" s="288" t="s">
-        <v>85</v>
-      </c>
+      <c r="F12" s="288"/>
       <c r="G12" s="289"/>
       <c r="H12" s="289"/>
       <c r="I12" s="290"/>
-      <c r="J12" s="55">
-        <v>1</v>
-      </c>
-      <c r="K12" s="55" t="s">
-        <v>54</v>
-      </c>
-      <c r="L12" s="291" t="s">
-        <v>86</v>
-      </c>
+      <c r="J12" s="55"/>
+      <c r="K12" s="55"/>
+      <c r="L12" s="291"/>
       <c r="M12" s="292"/>
       <c r="N12" s="292"/>
       <c r="O12" s="292"/>
@@ -11218,7 +11187,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -11514,7 +11483,7 @@
       <c r="X1" s="3"/>
       <c r="Y1" s="3"/>
     </row>
-    <row r="2" ht="21.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" ht="24.3" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="5" t="s">
         <v>1</v>
@@ -11574,7 +11543,7 @@
       <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="458" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="1"/>
@@ -11583,14 +11552,14 @@
       <c r="F4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="12"/>
+      <c r="G4" s="459"/>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
       <c r="J4" s="1"/>
       <c r="K4" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="L4" s="14"/>
+      <c r="L4" s="460"/>
       <c r="M4" s="15"/>
       <c r="N4" s="15"/>
       <c r="O4" s="15"/>
@@ -11636,21 +11605,21 @@
       <c r="A6" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="18"/>
+      <c r="B6" s="459"/>
       <c r="C6" s="1"/>
       <c r="D6" s="2"/>
       <c r="E6" s="19"/>
       <c r="F6" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="12"/>
+      <c r="G6" s="459"/>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
       <c r="J6" s="1"/>
       <c r="K6" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="L6" s="20" t="s">
+      <c r="L6" s="461" t="s">
         <v>9</v>
       </c>
       <c r="M6" s="20"/>
@@ -14209,7 +14178,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -15002,7 +14971,7 @@
       <c r="A6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="472" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="3"/>
@@ -15012,13 +14981,13 @@
       <c r="G6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="H6" s="8"/>
+      <c r="H6" s="168"/>
       <c r="I6" s="8"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="207"/>
+      <c r="L6" s="473"/>
       <c r="M6" s="8"/>
       <c r="N6" s="1"/>
       <c r="O6" s="3"/>
@@ -15064,7 +15033,7 @@
       <c r="A8" s="190" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="472" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="3"/>
@@ -15074,13 +15043,13 @@
       <c r="G8" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H8" s="8"/>
+      <c r="H8" s="168"/>
       <c r="I8" s="8"/>
       <c r="J8" s="3"/>
       <c r="K8" s="190" t="s">
         <v>42</v>
       </c>
-      <c r="L8" s="8"/>
+      <c r="L8" s="168"/>
       <c r="M8" s="8"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
@@ -15122,7 +15091,7 @@
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
     </row>
-    <row r="10" ht="14.45" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="208" t="s">
         <v>43</v>
       </c>
@@ -15167,7 +15136,7 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
     </row>
-    <row r="11" ht="14.45" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="212"/>
       <c r="B11" s="213"/>
       <c r="C11" s="214"/>
@@ -15209,7 +15178,7 @@
       <c r="J12" s="222"/>
       <c r="K12" s="216"/>
       <c r="L12" s="216"/>
-      <c r="M12" s="223"/>
+      <c r="M12" s="474"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
@@ -15236,7 +15205,7 @@
       <c r="J13" s="228"/>
       <c r="K13" s="224"/>
       <c r="L13" s="224"/>
-      <c r="M13" s="230"/>
+      <c r="M13" s="475"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
@@ -15263,7 +15232,7 @@
       <c r="J14" s="228"/>
       <c r="K14" s="224"/>
       <c r="L14" s="224"/>
-      <c r="M14" s="230"/>
+      <c r="M14" s="475"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
@@ -15967,7 +15936,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -16696,7 +16665,7 @@
       <c r="A6" s="190" t="s">
         <v>59</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="472" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="3"/>
@@ -16708,7 +16677,7 @@
         <v>38</v>
       </c>
       <c r="I6" s="8"/>
-      <c r="J6" s="8" t="s">
+      <c r="J6" s="168" t="s">
         <v>60</v>
       </c>
       <c r="K6" s="8"/>
@@ -16718,7 +16687,7 @@
       <c r="O6" s="190" t="s">
         <v>61</v>
       </c>
-      <c r="P6" s="207">
+      <c r="P6" s="473">
         <v>46219</v>
       </c>
       <c r="Q6" s="8"/>
@@ -16762,7 +16731,7 @@
       <c r="A8" s="190" t="s">
         <v>62</v>
       </c>
-      <c r="B8" s="190" t="s">
+      <c r="B8" s="168" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="190"/>
@@ -16774,7 +16743,7 @@
         <v>63</v>
       </c>
       <c r="I8" s="8"/>
-      <c r="J8" s="8" t="s">
+      <c r="J8" s="168" t="s">
         <v>64</v>
       </c>
       <c r="K8" s="8"/>
@@ -16784,7 +16753,7 @@
       <c r="O8" s="190" t="s">
         <v>65</v>
       </c>
-      <c r="P8" s="8">
+      <c r="P8" s="168">
         <v>7</v>
       </c>
       <c r="Q8" s="8"/>
@@ -16824,7 +16793,7 @@
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
     </row>
-    <row r="10" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="208" t="s">
         <v>11</v>
       </c>
@@ -16865,7 +16834,7 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
     </row>
-    <row r="11" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="212"/>
       <c r="B11" s="212"/>
       <c r="C11" s="264"/>
@@ -16895,32 +16864,18 @@
       <c r="Y11" s="3"/>
     </row>
     <row r="12" ht="22.15" customHeight="1" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="267" t="s">
-        <v>71</v>
-      </c>
-      <c r="B12" s="267" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" s="169" t="s">
-        <v>73</v>
-      </c>
+      <c r="A12" s="267"/>
+      <c r="B12" s="267"/>
+      <c r="C12" s="169"/>
       <c r="D12" s="268"/>
       <c r="E12" s="172"/>
-      <c r="F12" s="192" t="s">
-        <v>74</v>
-      </c>
+      <c r="F12" s="192"/>
       <c r="G12" s="56"/>
       <c r="H12" s="56"/>
       <c r="I12" s="58"/>
-      <c r="J12" s="55">
-        <v>1</v>
-      </c>
-      <c r="K12" s="55" t="s">
-        <v>54</v>
-      </c>
-      <c r="L12" s="267" t="s">
-        <v>75</v>
-      </c>
+      <c r="J12" s="55"/>
+      <c r="K12" s="55"/>
+      <c r="L12" s="267"/>
       <c r="M12" s="267"/>
       <c r="N12" s="267"/>
       <c r="O12" s="267"/>
@@ -17633,7 +17588,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -17797,7 +17752,7 @@
       <c r="A6" s="42" t="s">
         <v>88</v>
       </c>
-      <c r="B6" s="283" t="s">
+      <c r="B6" s="483" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="283"/>
@@ -17806,7 +17761,7 @@
         <v>89</v>
       </c>
       <c r="F6" s="295"/>
-      <c r="G6" s="95" t="s">
+      <c r="G6" s="484" t="s">
         <v>60</v>
       </c>
       <c r="H6" s="95"/>
@@ -17814,7 +17769,7 @@
       <c r="J6" s="295" t="s">
         <v>90</v>
       </c>
-      <c r="K6" s="296">
+      <c r="K6" s="485">
         <v>46219</v>
       </c>
       <c r="L6" s="95"/>
@@ -17864,23 +17819,19 @@
         <v>91</v>
       </c>
       <c r="B8" s="256"/>
-      <c r="C8" s="42" t="s">
-        <v>73</v>
-      </c>
+      <c r="C8" s="486"/>
       <c r="D8" s="42"/>
       <c r="E8" s="295" t="s">
         <v>92</v>
       </c>
       <c r="F8" s="295"/>
-      <c r="G8" s="95" t="s">
-        <v>93</v>
-      </c>
+      <c r="G8" s="484"/>
       <c r="H8" s="95"/>
       <c r="I8" s="42"/>
       <c r="J8" s="295" t="s">
         <v>94</v>
       </c>
-      <c r="K8" s="95">
+      <c r="K8" s="484">
         <v>20</v>
       </c>
       <c r="L8" s="95">
@@ -17907,9 +17858,7 @@
         <v>95</v>
       </c>
       <c r="B9" s="256"/>
-      <c r="C9" s="42" t="s">
-        <v>72</v>
-      </c>
+      <c r="C9" s="42"/>
       <c r="D9" s="42"/>
       <c r="E9" s="42"/>
       <c r="F9" s="42"/>
@@ -18562,7 +18511,7 @@
       </c>
       <c r="B33" s="305"/>
       <c r="C33" s="305"/>
-      <c r="D33" s="306"/>
+      <c r="D33" s="487"/>
       <c r="E33" s="306"/>
       <c r="F33" s="306"/>
       <c r="G33" s="306"/>
@@ -18616,9 +18565,7 @@
     </row>
     <row r="35" ht="21.95" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="307"/>
-      <c r="B35" s="309" t="s">
-        <v>75</v>
-      </c>
+      <c r="B35" s="309"/>
       <c r="C35" s="309"/>
       <c r="D35" s="309"/>
       <c r="E35" s="309"/>
@@ -19307,7 +19254,7 @@
       <c r="A58" s="42" t="s">
         <v>88</v>
       </c>
-      <c r="B58" s="283" t="s">
+      <c r="B58" s="483" t="s">
         <v>3</v>
       </c>
       <c r="C58" s="283"/>
@@ -19316,7 +19263,7 @@
         <v>89</v>
       </c>
       <c r="F58" s="295"/>
-      <c r="G58" s="95" t="s">
+      <c r="G58" s="484" t="s">
         <v>79</v>
       </c>
       <c r="H58" s="95"/>
@@ -19324,7 +19271,7 @@
       <c r="J58" s="295" t="s">
         <v>90</v>
       </c>
-      <c r="K58" s="296">
+      <c r="K58" s="485">
         <v>46220</v>
       </c>
       <c r="L58" s="95"/>
@@ -19374,23 +19321,19 @@
         <v>91</v>
       </c>
       <c r="B60" s="256"/>
-      <c r="C60" s="42" t="s">
-        <v>84</v>
-      </c>
+      <c r="C60" s="486"/>
       <c r="D60" s="42"/>
       <c r="E60" s="295" t="s">
         <v>92</v>
       </c>
       <c r="F60" s="295"/>
-      <c r="G60" s="95" t="s">
-        <v>126</v>
-      </c>
+      <c r="G60" s="484"/>
       <c r="H60" s="95"/>
       <c r="I60" s="42"/>
       <c r="J60" s="295" t="s">
         <v>94</v>
       </c>
-      <c r="K60" s="95">
+      <c r="K60" s="484">
         <v>20</v>
       </c>
       <c r="L60" s="95">
@@ -19417,9 +19360,7 @@
         <v>95</v>
       </c>
       <c r="B61" s="256"/>
-      <c r="C61" s="42" t="s">
-        <v>72</v>
-      </c>
+      <c r="C61" s="42"/>
       <c r="D61" s="42"/>
       <c r="E61" s="42"/>
       <c r="F61" s="42"/>
@@ -20072,7 +20013,7 @@
       </c>
       <c r="B85" s="305"/>
       <c r="C85" s="305"/>
-      <c r="D85" s="306"/>
+      <c r="D85" s="487"/>
       <c r="E85" s="306"/>
       <c r="F85" s="306"/>
       <c r="G85" s="306"/>
@@ -20126,9 +20067,7 @@
     </row>
     <row r="87" ht="21.95" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="307"/>
-      <c r="B87" s="309" t="s">
-        <v>127</v>
-      </c>
+      <c r="B87" s="309"/>
       <c r="C87" s="309"/>
       <c r="D87" s="309"/>
       <c r="E87" s="309"/>
@@ -20888,7 +20827,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -21681,7 +21620,7 @@
       <c r="A6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="472" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="3"/>
@@ -21691,13 +21630,13 @@
       <c r="G6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="H6" s="8"/>
+      <c r="H6" s="168"/>
       <c r="I6" s="8"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="207"/>
+      <c r="L6" s="473"/>
       <c r="M6" s="8"/>
       <c r="N6" s="1"/>
       <c r="O6" s="3"/>
@@ -21743,7 +21682,7 @@
       <c r="A8" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="472" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="270"/>
@@ -21753,13 +21692,13 @@
       <c r="G8" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H8" s="8"/>
+      <c r="H8" s="168"/>
       <c r="I8" s="8"/>
       <c r="J8" s="3"/>
       <c r="K8" s="190" t="s">
         <v>42</v>
       </c>
-      <c r="L8" s="8"/>
+      <c r="L8" s="168"/>
       <c r="M8" s="8"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
@@ -21801,7 +21740,7 @@
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
     </row>
-    <row r="10" ht="14.45" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="208" t="s">
         <v>43</v>
       </c>
@@ -21846,7 +21785,7 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
     </row>
-    <row r="11" ht="14.45" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="212"/>
       <c r="B11" s="213"/>
       <c r="C11" s="214"/>
@@ -21880,15 +21819,15 @@
       <c r="B12" s="216"/>
       <c r="C12" s="216"/>
       <c r="D12" s="217"/>
-      <c r="E12" s="271"/>
-      <c r="F12" s="272"/>
+      <c r="E12" s="476"/>
+      <c r="F12" s="477"/>
       <c r="G12" s="216"/>
       <c r="H12" s="222"/>
       <c r="I12" s="273"/>
       <c r="J12" s="274"/>
       <c r="K12" s="216"/>
       <c r="L12" s="216"/>
-      <c r="M12" s="275"/>
+      <c r="M12" s="478"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
@@ -21907,15 +21846,15 @@
       <c r="B13" s="247"/>
       <c r="C13" s="247"/>
       <c r="D13" s="225"/>
-      <c r="E13" s="276"/>
-      <c r="F13" s="277"/>
+      <c r="E13" s="479"/>
+      <c r="F13" s="480"/>
       <c r="G13" s="224"/>
       <c r="H13" s="278"/>
       <c r="I13" s="279"/>
       <c r="J13" s="228"/>
       <c r="K13" s="224"/>
       <c r="L13" s="224"/>
-      <c r="M13" s="280"/>
+      <c r="M13" s="481"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
@@ -21934,15 +21873,15 @@
       <c r="B14" s="247"/>
       <c r="C14" s="247"/>
       <c r="D14" s="225"/>
-      <c r="E14" s="276"/>
-      <c r="F14" s="277"/>
+      <c r="E14" s="479"/>
+      <c r="F14" s="480"/>
       <c r="G14" s="224"/>
       <c r="H14" s="278"/>
       <c r="I14" s="279"/>
       <c r="J14" s="228"/>
       <c r="K14" s="224"/>
       <c r="L14" s="224"/>
-      <c r="M14" s="280"/>
+      <c r="M14" s="481"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
@@ -21961,15 +21900,15 @@
       <c r="B15" s="247"/>
       <c r="C15" s="247"/>
       <c r="D15" s="225"/>
-      <c r="E15" s="276"/>
-      <c r="F15" s="277"/>
+      <c r="E15" s="479"/>
+      <c r="F15" s="480"/>
       <c r="G15" s="224"/>
       <c r="H15" s="278"/>
       <c r="I15" s="279"/>
       <c r="J15" s="228"/>
       <c r="K15" s="224"/>
       <c r="L15" s="224"/>
-      <c r="M15" s="280"/>
+      <c r="M15" s="481"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
@@ -21988,15 +21927,15 @@
       <c r="B16" s="247"/>
       <c r="C16" s="247"/>
       <c r="D16" s="225"/>
-      <c r="E16" s="276"/>
-      <c r="F16" s="277"/>
+      <c r="E16" s="479"/>
+      <c r="F16" s="480"/>
       <c r="G16" s="224"/>
       <c r="H16" s="278"/>
       <c r="I16" s="279"/>
       <c r="J16" s="228"/>
       <c r="K16" s="224"/>
       <c r="L16" s="224"/>
-      <c r="M16" s="280"/>
+      <c r="M16" s="481"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
@@ -22015,15 +21954,15 @@
       <c r="B17" s="224"/>
       <c r="C17" s="224"/>
       <c r="D17" s="225"/>
-      <c r="E17" s="276"/>
-      <c r="F17" s="277"/>
+      <c r="E17" s="479"/>
+      <c r="F17" s="480"/>
       <c r="G17" s="224"/>
       <c r="H17" s="278"/>
       <c r="I17" s="279"/>
       <c r="J17" s="228"/>
       <c r="K17" s="224"/>
       <c r="L17" s="224"/>
-      <c r="M17" s="280"/>
+      <c r="M17" s="481"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
@@ -22038,19 +21977,19 @@
       <c r="Y17" s="3"/>
     </row>
     <row r="18" ht="22.15" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A18" s="281"/>
+      <c r="A18" s="482"/>
       <c r="B18" s="247"/>
       <c r="C18" s="247"/>
       <c r="D18" s="225"/>
-      <c r="E18" s="276"/>
-      <c r="F18" s="277"/>
+      <c r="E18" s="479"/>
+      <c r="F18" s="480"/>
       <c r="G18" s="224"/>
       <c r="H18" s="278"/>
       <c r="I18" s="279"/>
       <c r="J18" s="228"/>
       <c r="K18" s="224"/>
       <c r="L18" s="224"/>
-      <c r="M18" s="280"/>
+      <c r="M18" s="481"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
@@ -22638,7 +22577,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y22"/>
   <sheetFormatPr defaultRowHeight="12" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="7.5" customHeight="1"/>
   <cols>
@@ -24315,9 +24254,9 @@
       <c r="I11" s="452"/>
       <c r="J11" s="452"/>
       <c r="K11" s="452"/>
-      <c r="L11" s="455"/>
-      <c r="M11" s="455"/>
-      <c r="N11" s="455"/>
+      <c r="L11" s="490"/>
+      <c r="M11" s="490"/>
+      <c r="N11" s="490"/>
       <c r="O11" s="419"/>
       <c r="P11" s="419"/>
       <c r="Q11" s="416"/>
@@ -24342,9 +24281,9 @@
       <c r="I12" s="452"/>
       <c r="J12" s="452"/>
       <c r="K12" s="452"/>
-      <c r="L12" s="455"/>
-      <c r="M12" s="455"/>
-      <c r="N12" s="455"/>
+      <c r="L12" s="490"/>
+      <c r="M12" s="490"/>
+      <c r="N12" s="490"/>
       <c r="O12" s="419"/>
       <c r="P12" s="419"/>
       <c r="Q12" s="416"/>
@@ -24369,9 +24308,9 @@
       <c r="I13" s="452"/>
       <c r="J13" s="452"/>
       <c r="K13" s="452"/>
-      <c r="L13" s="455"/>
-      <c r="M13" s="455"/>
-      <c r="N13" s="455"/>
+      <c r="L13" s="490"/>
+      <c r="M13" s="490"/>
+      <c r="N13" s="490"/>
       <c r="O13" s="419"/>
       <c r="P13" s="419"/>
       <c r="Q13" s="416"/>
@@ -24396,9 +24335,9 @@
       <c r="I14" s="452"/>
       <c r="J14" s="452"/>
       <c r="K14" s="452"/>
-      <c r="L14" s="455"/>
-      <c r="M14" s="455"/>
-      <c r="N14" s="455"/>
+      <c r="L14" s="490"/>
+      <c r="M14" s="490"/>
+      <c r="N14" s="490"/>
       <c r="O14" s="419"/>
       <c r="P14" s="419"/>
       <c r="Q14" s="416"/>
@@ -24423,9 +24362,9 @@
       <c r="I15" s="452"/>
       <c r="J15" s="452"/>
       <c r="K15" s="452"/>
-      <c r="L15" s="455"/>
-      <c r="M15" s="455"/>
-      <c r="N15" s="455"/>
+      <c r="L15" s="490"/>
+      <c r="M15" s="490"/>
+      <c r="N15" s="490"/>
       <c r="O15" s="419"/>
       <c r="P15" s="419"/>
       <c r="Q15" s="416"/>
@@ -24450,9 +24389,9 @@
       <c r="I16" s="452"/>
       <c r="J16" s="452"/>
       <c r="K16" s="452"/>
-      <c r="L16" s="455"/>
-      <c r="M16" s="455"/>
-      <c r="N16" s="455"/>
+      <c r="L16" s="490"/>
+      <c r="M16" s="490"/>
+      <c r="N16" s="490"/>
       <c r="O16" s="419"/>
       <c r="P16" s="419"/>
       <c r="Q16" s="416"/>
@@ -24477,9 +24416,9 @@
       <c r="I17" s="452"/>
       <c r="J17" s="452"/>
       <c r="K17" s="452"/>
-      <c r="L17" s="455"/>
-      <c r="M17" s="455"/>
-      <c r="N17" s="455"/>
+      <c r="L17" s="490"/>
+      <c r="M17" s="490"/>
+      <c r="N17" s="490"/>
       <c r="O17" s="419"/>
       <c r="P17" s="419"/>
       <c r="Q17" s="416"/>
@@ -24650,7 +24589,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -25317,11 +25256,11 @@
       <c r="A6" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="9"/>
+      <c r="B6" s="458"/>
       <c r="C6" s="157" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="15"/>
+      <c r="D6" s="462"/>
       <c r="E6" s="15"/>
       <c r="F6" s="9"/>
       <c r="G6" s="158" t="s">
@@ -25380,17 +25319,17 @@
       <c r="A8" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="160"/>
+      <c r="B8" s="462"/>
       <c r="C8" s="157" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="15"/>
+      <c r="D8" s="462"/>
       <c r="E8" s="15"/>
       <c r="F8" s="157"/>
       <c r="G8" s="161" t="s">
         <v>30</v>
       </c>
-      <c r="H8" s="20"/>
+      <c r="H8" s="461"/>
       <c r="I8" s="9"/>
       <c r="J8" s="9"/>
       <c r="K8" s="9"/>
@@ -25528,7 +25467,7 @@
         <v>34</v>
       </c>
       <c r="B13" s="166"/>
-      <c r="C13" s="167"/>
+      <c r="C13" s="463"/>
       <c r="D13" s="167"/>
       <c r="E13" s="167"/>
       <c r="F13" s="167"/>
@@ -25555,7 +25494,7 @@
     <row r="14" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="169"/>
       <c r="B14" s="170"/>
-      <c r="C14" s="171"/>
+      <c r="C14" s="464"/>
       <c r="D14" s="171"/>
       <c r="E14" s="171"/>
       <c r="F14" s="171"/>
@@ -25582,7 +25521,7 @@
     <row r="15" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="169"/>
       <c r="B15" s="172"/>
-      <c r="C15" s="173"/>
+      <c r="C15" s="465"/>
       <c r="D15" s="173"/>
       <c r="E15" s="173"/>
       <c r="F15" s="173"/>
@@ -25609,7 +25548,7 @@
     <row r="16" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="174"/>
       <c r="B16" s="172"/>
-      <c r="C16" s="173"/>
+      <c r="C16" s="465"/>
       <c r="D16" s="173"/>
       <c r="E16" s="173"/>
       <c r="F16" s="173"/>
@@ -25636,7 +25575,7 @@
     <row r="17" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" s="175"/>
       <c r="B17" s="176"/>
-      <c r="C17" s="177"/>
+      <c r="C17" s="466"/>
       <c r="D17" s="178"/>
       <c r="E17" s="178"/>
       <c r="F17" s="178"/>
@@ -25663,7 +25602,7 @@
     <row r="18" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="180"/>
       <c r="B18" s="29"/>
-      <c r="C18" s="181"/>
+      <c r="C18" s="467"/>
       <c r="D18" s="182"/>
       <c r="E18" s="182"/>
       <c r="F18" s="182"/>
@@ -25690,7 +25629,7 @@
     <row r="19" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" s="184"/>
       <c r="B19" s="172"/>
-      <c r="C19" s="185"/>
+      <c r="C19" s="468"/>
       <c r="D19" s="186"/>
       <c r="E19" s="186"/>
       <c r="F19" s="186"/>
@@ -25717,7 +25656,7 @@
     <row r="20" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" s="169"/>
       <c r="B20" s="188"/>
-      <c r="C20" s="185"/>
+      <c r="C20" s="468"/>
       <c r="D20" s="186"/>
       <c r="E20" s="186"/>
       <c r="F20" s="186"/>
@@ -25744,7 +25683,7 @@
     <row r="21" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" s="189"/>
       <c r="B21" s="172"/>
-      <c r="C21" s="185"/>
+      <c r="C21" s="468"/>
       <c r="D21" s="186"/>
       <c r="E21" s="186"/>
       <c r="F21" s="186"/>
@@ -25771,7 +25710,7 @@
     <row r="22" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" s="191"/>
       <c r="B22" s="176"/>
-      <c r="C22" s="173"/>
+      <c r="C22" s="465"/>
       <c r="D22" s="173"/>
       <c r="E22" s="173"/>
       <c r="F22" s="173"/>
@@ -25798,7 +25737,7 @@
     <row r="23" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" s="180"/>
       <c r="B23" s="188"/>
-      <c r="C23" s="181"/>
+      <c r="C23" s="467"/>
       <c r="D23" s="182"/>
       <c r="E23" s="182"/>
       <c r="F23" s="182"/>
@@ -25825,7 +25764,7 @@
     <row r="24" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" s="192"/>
       <c r="B24" s="170"/>
-      <c r="C24" s="173"/>
+      <c r="C24" s="465"/>
       <c r="D24" s="173"/>
       <c r="E24" s="173"/>
       <c r="F24" s="173"/>
@@ -25852,7 +25791,7 @@
     <row r="25" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" s="174"/>
       <c r="B25" s="170"/>
-      <c r="C25" s="193"/>
+      <c r="C25" s="469"/>
       <c r="D25" s="194"/>
       <c r="E25" s="194"/>
       <c r="F25" s="194"/>
@@ -25879,7 +25818,7 @@
     <row r="26" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" s="169"/>
       <c r="B26" s="172"/>
-      <c r="C26" s="173"/>
+      <c r="C26" s="465"/>
       <c r="D26" s="173"/>
       <c r="E26" s="173"/>
       <c r="F26" s="173"/>
@@ -25906,7 +25845,7 @@
     <row r="27" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" s="196"/>
       <c r="B27" s="197"/>
-      <c r="C27" s="177"/>
+      <c r="C27" s="466"/>
       <c r="D27" s="178"/>
       <c r="E27" s="178"/>
       <c r="F27" s="178"/>
@@ -25933,7 +25872,7 @@
     <row r="28" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" s="31"/>
       <c r="B28" s="188"/>
-      <c r="C28" s="198"/>
+      <c r="C28" s="470"/>
       <c r="D28" s="198"/>
       <c r="E28" s="198"/>
       <c r="F28" s="198"/>
@@ -25960,7 +25899,7 @@
     <row r="29" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" s="169"/>
       <c r="B29" s="172"/>
-      <c r="C29" s="173"/>
+      <c r="C29" s="465"/>
       <c r="D29" s="173"/>
       <c r="E29" s="173"/>
       <c r="F29" s="173"/>
@@ -25987,7 +25926,7 @@
     <row r="30" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" s="189"/>
       <c r="B30" s="172"/>
-      <c r="C30" s="199"/>
+      <c r="C30" s="471"/>
       <c r="D30" s="194"/>
       <c r="E30" s="194"/>
       <c r="F30" s="194"/>
@@ -26014,7 +25953,7 @@
     <row r="31" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" s="200"/>
       <c r="B31" s="172"/>
-      <c r="C31" s="173"/>
+      <c r="C31" s="465"/>
       <c r="D31" s="173"/>
       <c r="E31" s="173"/>
       <c r="F31" s="173"/>
@@ -26041,7 +25980,7 @@
     <row r="32" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" s="175"/>
       <c r="B32" s="197"/>
-      <c r="C32" s="177"/>
+      <c r="C32" s="466"/>
       <c r="D32" s="178"/>
       <c r="E32" s="178"/>
       <c r="F32" s="178"/>
@@ -26068,7 +26007,7 @@
     <row r="33" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" s="180"/>
       <c r="B33" s="29"/>
-      <c r="C33" s="181"/>
+      <c r="C33" s="467"/>
       <c r="D33" s="182"/>
       <c r="E33" s="182"/>
       <c r="F33" s="182"/>
@@ -26097,7 +26036,7 @@
         <v>35</v>
       </c>
       <c r="B34" s="172"/>
-      <c r="C34" s="199"/>
+      <c r="C34" s="471"/>
       <c r="D34" s="194"/>
       <c r="E34" s="194"/>
       <c r="F34" s="194"/>
@@ -26124,7 +26063,7 @@
     <row r="35" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35" s="189"/>
       <c r="B35" s="188"/>
-      <c r="C35" s="198"/>
+      <c r="C35" s="470"/>
       <c r="D35" s="198"/>
       <c r="E35" s="198"/>
       <c r="F35" s="198"/>
@@ -26151,7 +26090,7 @@
     <row r="36" ht="20.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36" s="184"/>
       <c r="B36" s="188"/>
-      <c r="C36" s="198"/>
+      <c r="C36" s="470"/>
       <c r="D36" s="198"/>
       <c r="E36" s="198"/>
       <c r="F36" s="198"/>
@@ -26178,7 +26117,7 @@
     <row r="37" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" s="201"/>
       <c r="B37" s="197"/>
-      <c r="C37" s="177"/>
+      <c r="C37" s="466"/>
       <c r="D37" s="178"/>
       <c r="E37" s="178"/>
       <c r="F37" s="178"/>
@@ -26205,7 +26144,7 @@
     <row r="38" ht="20.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38" s="192"/>
       <c r="B38" s="188"/>
-      <c r="C38" s="193"/>
+      <c r="C38" s="469"/>
       <c r="D38" s="194"/>
       <c r="E38" s="194"/>
       <c r="F38" s="194"/>
@@ -26232,7 +26171,7 @@
     <row r="39" ht="20.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39" s="174"/>
       <c r="B39" s="188"/>
-      <c r="C39" s="185"/>
+      <c r="C39" s="468"/>
       <c r="D39" s="186"/>
       <c r="E39" s="186"/>
       <c r="F39" s="186"/>
@@ -26259,7 +26198,7 @@
     <row r="40" ht="20.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40" s="169"/>
       <c r="B40" s="172"/>
-      <c r="C40" s="173"/>
+      <c r="C40" s="465"/>
       <c r="D40" s="173"/>
       <c r="E40" s="173"/>
       <c r="F40" s="173"/>
@@ -26286,7 +26225,7 @@
     <row r="41" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41" s="200"/>
       <c r="B41" s="188"/>
-      <c r="C41" s="198"/>
+      <c r="C41" s="470"/>
       <c r="D41" s="198"/>
       <c r="E41" s="198"/>
       <c r="F41" s="198"/>
@@ -26313,7 +26252,7 @@
     <row r="42" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42" s="192"/>
       <c r="B42" s="58"/>
-      <c r="C42" s="173"/>
+      <c r="C42" s="465"/>
       <c r="D42" s="173"/>
       <c r="E42" s="173"/>
       <c r="F42" s="173"/>
@@ -26583,7 +26522,7 @@
       <c r="Y51" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="41">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="C3:F3"/>
@@ -26623,6 +26562,8 @@
     <mergeCell ref="C42:H42"/>
     <mergeCell ref="A46:B46"/>
     <mergeCell ref="G46:H46"/>
+    <mergeCell ref="C43:H43"/>
+    <mergeCell ref="C44:H44"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.3937007874015748" bottom="0.3937007874015748" header="0.5118110236220472" footer="0.31496062992125984"/>
@@ -26631,7 +26572,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -27304,7 +27245,7 @@
       <c r="A4" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B4" s="190" t="s">
+      <c r="B4" s="168" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="190"/>
@@ -27313,7 +27254,7 @@
       <c r="F4" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="G4" s="207"/>
+      <c r="G4" s="473"/>
       <c r="H4" s="8"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
@@ -27364,7 +27305,7 @@
       <c r="A6" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="168" t="s">
         <v>60</v>
       </c>
       <c r="C6" s="8"/>
@@ -27375,7 +27316,7 @@
       <c r="F6" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="G6" s="330" t="s">
+      <c r="G6" s="488" t="s">
         <v>25</v>
       </c>
       <c r="H6" s="3"/>
@@ -28018,12 +27959,12 @@
     <row r="29" ht="21.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" s="355"/>
       <c r="B29" s="356"/>
-      <c r="C29" s="357"/>
-      <c r="D29" s="357"/>
-      <c r="E29" s="357"/>
-      <c r="F29" s="357"/>
-      <c r="G29" s="357"/>
-      <c r="H29" s="357"/>
+      <c r="C29" s="489"/>
+      <c r="D29" s="489"/>
+      <c r="E29" s="489"/>
+      <c r="F29" s="489"/>
+      <c r="G29" s="489"/>
+      <c r="H29" s="489"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
@@ -28045,12 +27986,12 @@
     <row r="30" ht="21.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" s="355"/>
       <c r="B30" s="356"/>
-      <c r="C30" s="357"/>
-      <c r="D30" s="357"/>
-      <c r="E30" s="357"/>
-      <c r="F30" s="357"/>
-      <c r="G30" s="357"/>
-      <c r="H30" s="357"/>
+      <c r="C30" s="489"/>
+      <c r="D30" s="489"/>
+      <c r="E30" s="489"/>
+      <c r="F30" s="489"/>
+      <c r="G30" s="489"/>
+      <c r="H30" s="489"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
@@ -28072,12 +28013,12 @@
     <row r="31" ht="21.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" s="355"/>
       <c r="B31" s="356"/>
-      <c r="C31" s="357"/>
-      <c r="D31" s="357"/>
-      <c r="E31" s="357"/>
-      <c r="F31" s="357"/>
-      <c r="G31" s="357"/>
-      <c r="H31" s="357"/>
+      <c r="C31" s="489"/>
+      <c r="D31" s="489"/>
+      <c r="E31" s="489"/>
+      <c r="F31" s="489"/>
+      <c r="G31" s="489"/>
+      <c r="H31" s="489"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
@@ -28376,7 +28317,7 @@
       <c r="F41" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="G41" s="207">
+      <c r="G41" s="473">
         <v>46220</v>
       </c>
       <c r="H41" s="8"/>
@@ -28429,7 +28370,7 @@
       <c r="A43" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="168" t="s">
         <v>79</v>
       </c>
       <c r="C43" s="8"/>
@@ -28440,7 +28381,7 @@
       <c r="F43" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="G43" s="330" t="s">
+      <c r="G43" s="488" t="s">
         <v>25</v>
       </c>
       <c r="H43" s="3"/>
@@ -28622,24 +28563,14 @@
       <c r="Y48" s="3"/>
     </row>
     <row r="49" ht="21.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A49" s="338" t="s">
-        <v>145</v>
-      </c>
+      <c r="A49" s="338"/>
       <c r="B49" s="338"/>
-      <c r="C49" s="361" t="s">
-        <v>146</v>
-      </c>
-      <c r="D49" s="247" t="s">
-        <v>14</v>
-      </c>
+      <c r="C49" s="361"/>
+      <c r="D49" s="247"/>
       <c r="E49" s="247"/>
-      <c r="F49" s="362" t="s">
-        <v>147</v>
-      </c>
+      <c r="F49" s="362"/>
       <c r="G49" s="247"/>
-      <c r="H49" s="247" t="s">
-        <v>72</v>
-      </c>
+      <c r="H49" s="247"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3"/>
       <c r="K49" s="3"/>
